--- a/test-data/receipts.xlsx
+++ b/test-data/receipts.xlsx
@@ -404,16 +404,16 @@
         <v>Fecha</v>
       </c>
       <c r="B1" t="str">
-        <v>Número</v>
+        <v>Número de Recibo</v>
       </c>
       <c r="C1" t="str">
-        <v>Entidad (Nombre o CUIT)</v>
+        <v>Cliente (Nombre o CUIT)</v>
       </c>
       <c r="D1" t="str">
         <v>Monto Total</v>
       </c>
       <c r="E1" t="str">
-        <v>Medio</v>
+        <v>Medio de Pago</v>
       </c>
       <c r="F1" t="str">
         <v>Banco</v>
